--- a/data/trans_dic/P1805_2016_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1805_2016_2023-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,44</t>
+          <t>0,56; 2,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,23</t>
+          <t>1,42; 4,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,52</t>
+          <t>1,66; 4,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,59</t>
+          <t>1,81; 3,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,92</t>
+          <t>1,31; 2,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,49</t>
+          <t>1,86; 3,55</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,56</t>
+          <t>1,0; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,0</t>
+          <t>1,36; 3,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,7</t>
+          <t>2,26; 4,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,85</t>
+          <t>2,67; 4,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,32</t>
+          <t>1,81; 3,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,47</t>
+          <t>2,32; 3,74</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,46</t>
+          <t>0,77; 2,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,49</t>
+          <t>2,23; 5,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,42</t>
+          <t>1,86; 4,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,17</t>
+          <t>3,77; 7,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,96</t>
+          <t>1,53; 3,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,34</t>
+          <t>3,34; 5,74</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,95</t>
+          <t>1,76; 3,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,19</t>
+          <t>3,41; 6,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,92</t>
+          <t>3,93; 6,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,3</t>
+          <t>4,06; 6,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,0</t>
+          <t>3,25; 5,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,08</t>
+          <t>4,1; 6,09</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,28</t>
+          <t>1,39; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,09</t>
+          <t>2,61; 4,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,54</t>
+          <t>3,07; 4,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,66</t>
+          <t>3,62; 4,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,22</t>
+          <t>2,37; 3,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,17</t>
+          <t>3,31; 4,26</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17342</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33242</t>
+          <t>36757</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3659; 16474</t>
+          <t>3803; 15734</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9119; 26879</t>
+          <t>9798; 28855</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11028; 30422</t>
+          <t>11158; 29305</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11771; 24264</t>
+          <t>13240; 25768</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17649; 39353</t>
+          <t>17704; 39156</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24462; 45725</t>
+          <t>26480; 50592</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>37952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56918</t>
+          <t>61952</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9985; 26168</t>
+          <t>10175; 27001</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9717; 35795</t>
+          <t>14314; 38156</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23966; 49037</t>
+          <t>23582; 48743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26288; 46476</t>
+          <t>28573; 50579</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39054; 68626</t>
+          <t>37388; 66546</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38092; 74574</t>
+          <t>49149; 79379</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26654</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38742</t>
+          <t>42065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65396</t>
+          <t>71181</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5292; 18680</t>
+          <t>5864; 18511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15974; 45739</t>
+          <t>17936; 45748</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14932; 34712</t>
+          <t>14567; 35364</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17900; 57583</t>
+          <t>30623; 56855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23285; 45791</t>
+          <t>23696; 46273</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41590; 87441</t>
+          <t>53910; 92668</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>46916</t>
+          <t>46466</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53262</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>100178</t>
+          <t>104468</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16436; 37024</t>
+          <t>16536; 37020</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33767; 66624</t>
+          <t>33767; 63797</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41503; 72199</t>
+          <t>41020; 71945</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39480; 68898</t>
+          <t>45443; 73730</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63331; 98988</t>
+          <t>64384; 100888</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79740; 122890</t>
+          <t>86372; 128457</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>157192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>255734</t>
+          <t>274357</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>47645; 77454</t>
+          <t>47184; 78455</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>83475; 141676</t>
+          <t>92163; 144233</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110010; 160910</t>
+          <t>108863; 155830</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114398; 170710</t>
+          <t>135152; 181297</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>167506; 223618</t>
+          <t>164728; 223541</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>220482; 297091</t>
+          <t>240328; 309782</t>
         </is>
       </c>
     </row>
